--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2876BE87-BE00-4B68-A9A5-B4D83D9A625B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587EBC81-6613-4380-ABD1-E98125C34168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14580" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,10 +31,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>レーザー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>PosX</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -83,25 +79,23 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>照射装置</t>
-    <rPh sb="0" eb="4">
-      <t>ショウシャソウチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>箱</t>
-    <rPh sb="0" eb="1">
-      <t>ハコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ミラー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゴール</t>
+    <t>Laser</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Device</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Box</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mirror</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Goal</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -463,45 +457,45 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>7.5</v>
@@ -541,14 +535,14 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>1</v>
+      <c r="A3" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -582,14 +576,14 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>1</v>
+      <c r="A4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -623,14 +617,14 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>1</v>
+      <c r="A5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -753,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -794,7 +788,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
         <v>-4</v>
@@ -835,7 +829,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
         <v>-4</v>
@@ -876,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
         <v>-4</v>
@@ -917,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="D12">
         <v>-4</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587EBC81-6613-4380-ABD1-E98125C34168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13218277-7E39-4168-A5B1-A1466F0250BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -539,13 +539,13 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>-7.5</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -580,13 +580,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -621,13 +621,13 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>-25</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -744,13 +744,13 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>-11.5</v>
       </c>
       <c r="C8">
         <v>0.5</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>-3.5</v>
       </c>
       <c r="C9">
         <v>0.5</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-2.5</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="C10">
         <v>0.5</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>6.5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -867,13 +867,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>12.5</v>
       </c>
       <c r="C11">
         <v>0.5</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="C12">
         <v>0.5</v>
       </c>
       <c r="D12">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="D14">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="E14">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13218277-7E39-4168-A5B1-A1466F0250BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4560A1-2C61-4DB0-88C0-4F2C4ED8E85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -662,19 +662,19 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-7.5</v>
+        <v>-6</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -700,16 +700,16 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>-12.5</v>
+        <v>-1</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>-7.5</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -741,34 +741,34 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>-11.5</v>
+        <v>-2</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -782,34 +782,34 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>-3.5</v>
+        <v>5.5</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D9">
-        <v>-2.5</v>
+        <v>4.5</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -826,13 +826,13 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="C10">
         <v>0.5</v>
       </c>
       <c r="D10">
-        <v>6.5</v>
+        <v>-10.5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -867,13 +867,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="C11">
         <v>0.5</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>-10.5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="C12">
         <v>0.5</v>
       </c>
       <c r="D12">
-        <v>-6.5</v>
+        <v>7.5</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -946,16 +946,16 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13">
-        <v>-2.5</v>
+        <v>1.5</v>
       </c>
       <c r="C13">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -967,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -987,16 +987,16 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>4.5</v>
+        <v>-10.5</v>
       </c>
       <c r="C14">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="D14">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1008,13 +1008,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1028,42 +1028,83 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>-13.5</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
+      </c>
+      <c r="D15">
+        <v>3.5</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
+      <c r="B16">
         <v>-1</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>3</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>17</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <v>0.01</v>
       </c>
-      <c r="I15">
+      <c r="I16">
         <v>0.01</v>
       </c>
-      <c r="J15">
+      <c r="J16">
         <v>0.01</v>
       </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4560A1-2C61-4DB0-88C0-4F2C4ED8E85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DA9E8D-2E95-4949-BA7D-592615312273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1108,6 +1108,88 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>-25</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4560A1-2C61-4DB0-88C0-4F2C4ED8E85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC437C0-D457-492A-89DF-280DADB53015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DA9E8D-2E95-4949-BA7D-592615312273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F68E5D7-2B69-4B23-8130-30EF2F8FD7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1108,88 +1108,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>2</v>
-      </c>
-      <c r="I17">
-        <v>2</v>
-      </c>
-      <c r="J17">
-        <v>2</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>-25</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>-1</v>
-      </c>
-      <c r="L18">
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F68E5D7-2B69-4B23-8130-30EF2F8FD7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91164B6-99C6-4E12-9D29-CB6EFD9C9EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -967,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1008,13 +1008,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1049,13 +1049,13 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K15">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91164B6-99C6-4E12-9D29-CB6EFD9C9EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05721EC4-B1CA-4B31-9118-A6117E44D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -545,7 +545,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="E3">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05721EC4-B1CA-4B31-9118-A6117E44D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED5AA7A-C54E-4A91-A495-CF2DA67A9FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-7.5</v>
+        <v>-6.5</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED5AA7A-C54E-4A91-A495-CF2DA67A9FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC2C0FD-ADD0-4B2D-B554-15DE8F50D1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -96,6 +96,10 @@
   </si>
   <si>
     <t>Goal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stairs</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -445,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1108,6 +1112,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC2C0FD-ADD0-4B2D-B554-15DE8F50D1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02AB532-5732-404B-B6A5-6A20B2049F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -707,10 +707,10 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="C7">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>-7.5</v>
@@ -725,13 +725,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="C8">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -789,10 +789,10 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="C9">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>4.5</v>
@@ -807,13 +807,13 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I17">
         <v>1</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02AB532-5732-404B-B6A5-6A20B2049F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB34C6A5-918C-40CB-A12E-06AFBF37C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>-7.5</v>
+        <v>-7</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-7</v>
+        <v>-7.5</v>
       </c>
       <c r="C8">
         <v>2</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB34C6A5-918C-40CB-A12E-06AFBF37C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB34C6A5-918C-40CB-A12E-06AFBF37C198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAC1053-2BD3-4A7A-95AC-E460F3C9F05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -836,7 +836,7 @@
         <v>0.5</v>
       </c>
       <c r="D10">
-        <v>-10.5</v>
+        <v>-7.5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1117,19 +1117,19 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1150,6 +1150,47 @@
         <v>0</v>
       </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>10.5</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0.5</v>
+      </c>
+      <c r="I18">
+        <v>0.5</v>
+      </c>
+      <c r="J18">
+        <v>0.5</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAC1053-2BD3-4A7A-95AC-E460F3C9F05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B490FB-57AB-4F8B-A644-051CECCC541F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -789,13 +789,13 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>7.5</v>
+        <v>-1.5</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="E9">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B490FB-57AB-4F8B-A644-051CECCC541F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F537CDC-8188-4B71-9184-7F061428DB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -833,7 +833,7 @@
         <v>3.5</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>-7.5</v>
@@ -874,7 +874,7 @@
         <v>11.5</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>-10.5</v>
@@ -915,7 +915,7 @@
         <v>10.5</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>7.5</v>
@@ -956,7 +956,7 @@
         <v>1.5</v>
       </c>
       <c r="C13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>10.5</v>
@@ -997,7 +997,7 @@
         <v>-10.5</v>
       </c>
       <c r="C14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>10.5</v>
@@ -1038,7 +1038,7 @@
         <v>-13.5</v>
       </c>
       <c r="C15">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>3.5</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F537CDC-8188-4B71-9184-7F061428DB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622A9D85-9090-43CE-AF43-953011844731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1161,7 +1161,7 @@
         <v>10.5</v>
       </c>
       <c r="C18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>2</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622A9D85-9090-43CE-AF43-953011844731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4B5DA5-BEEB-482D-9985-5DC07E72F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4B5DA5-BEEB-482D-9985-5DC07E72F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EE6AE6-EA97-4AAF-A5E5-45C36181FBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -505,7 +505,7 @@
         <v>7.5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -546,7 +546,7 @@
         <v>-6.5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>-25</v>
@@ -587,7 +587,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -628,7 +628,7 @@
         <v>-25</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>-7</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4B5DA5-BEEB-482D-9985-5DC07E72F410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA71B86B-3BB8-4AF2-B6FA-A6E8449D591E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
         <v>-6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>-7</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA71B86B-3BB8-4AF2-B6FA-A6E8449D591E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95A89D-DF2F-406D-93A4-458CD11F63E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95A89D-DF2F-406D-93A4-458CD11F63E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D201FB-852B-42B6-A62C-3FF32E294BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -505,7 +505,7 @@
         <v>7.5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -546,7 +546,7 @@
         <v>-6.5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>-25</v>
@@ -587,7 +587,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -628,7 +628,7 @@
         <v>-25</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>-7</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D201FB-852B-42B6-A62C-3FF32E294BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE96BCF2-395A-41DA-B2D9-24F25D08BD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
         <v>-6</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D6">
         <v>-7</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE96BCF2-395A-41DA-B2D9-24F25D08BD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80385B27-A0D9-4984-8185-CBB8A7E770FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1082,7 +1082,7 @@
         <v>3</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="E16">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80385B27-A0D9-4984-8185-CBB8A7E770FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1852A879-9056-40DF-93D7-3C77F3067D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5265" yWindow="1575" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1153,47 +1153,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>10.5</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0.5</v>
-      </c>
-      <c r="I18">
-        <v>0.5</v>
-      </c>
-      <c r="J18">
-        <v>0.5</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1852A879-9056-40DF-93D7-3C77F3067D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78A8119-FEAB-4D04-80F9-24C6F6AAB7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="1575" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1120,10 +1120,10 @@
         <v>10.5</v>
       </c>
       <c r="C17">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="D17">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="E17">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78A8119-FEAB-4D04-80F9-24C6F6AAB7CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0986C05F-E854-44CD-9CB6-54894E08DEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1120,10 +1120,10 @@
         <v>10.5</v>
       </c>
       <c r="C17">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="D17">
-        <v>-2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K17">
         <v>0</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0986C05F-E854-44CD-9CB6-54894E08DEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EB4A72-77FA-4A46-AFAA-08475C03D382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EB4A72-77FA-4A46-AFAA-08475C03D382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D93519-BC36-49E6-9AE4-127D82BE7AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -702,88 +702,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>-2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>-7</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>-7.5</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>90</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>16</v>

--- a/Data/Excel/stage1.xlsx
+++ b/Data/Excel/stage1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D93519-BC36-49E6-9AE4-127D82BE7AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4995BE92-214D-4052-B77F-A4762282E2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
